--- a/gm/resources/sample/loginConfig.xlsx
+++ b/gm/resources/sample/loginConfig.xlsx
@@ -105,7 +105,7 @@
     <t>int</t>
   </si>
   <si>
-    <t>map&lt;int{_}int&gt;{;}</t>
+    <t>map&lt;int{_}long&gt;{;}</t>
   </si>
   <si>
     <t>id</t>
@@ -329,12 +329,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/gm/resources/sample/loginConfig.xlsx
+++ b/gm/resources/sample/loginConfig.xlsx
@@ -123,7 +123,7 @@
     <t>google登入</t>
   </si>
   <si>
-    <t>1990000_1000000</t>
+    <t>1990000_199000</t>
   </si>
   <si>
     <t>ios登入</t>
@@ -329,12 +329,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/gm/resources/sample/loginConfig.xlsx
+++ b/gm/resources/sample/loginConfig.xlsx
@@ -123,7 +123,7 @@
     <t>google登入</t>
   </si>
   <si>
-    <t>1990000_199000</t>
+    <t>1990000_1400000</t>
   </si>
   <si>
     <t>ios登入</t>
@@ -1189,7 +1189,7 @@
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
     </row>
-    <row r="5" s="2" customFormat="1" spans="1:3">
+    <row r="5" s="2" customFormat="1" spans="1:4">
       <c r="A5" s="2">
         <v>1</v>
       </c>

--- a/gm/resources/sample/loginConfig.xlsx
+++ b/gm/resources/sample/loginConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="loginConfig" sheetId="1" r:id="rId1"/>
@@ -123,7 +123,7 @@
     <t>google登入</t>
   </si>
   <si>
-    <t>1990000_1400000</t>
+    <t>1990000_5200</t>
   </si>
   <si>
     <t>ios登入</t>

--- a/gm/resources/sample/loginConfig.xlsx
+++ b/gm/resources/sample/loginConfig.xlsx
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
   <si>
     <t>序号ID</t>
   </si>
@@ -123,7 +123,7 @@
     <t>google登入</t>
   </si>
   <si>
-    <t>1990000_5200</t>
+    <t>1990000_2000</t>
   </si>
   <si>
     <t>ios登入</t>
@@ -133,6 +133,9 @@
   </si>
   <si>
     <t>手机登入</t>
+  </si>
+  <si>
+    <t>1990000_8000</t>
   </si>
 </sst>
 </file>
@@ -1139,7 +1142,7 @@
   <cols>
     <col min="1" max="3" width="25.2916666666667" style="3" customWidth="1"/>
     <col min="4" max="4" width="27.6416666666667" style="3" customWidth="1"/>
-    <col min="5" max="5" width="9" style="3"/>
+    <col min="5" max="5" width="14.125" style="3"/>
     <col min="6" max="6" width="9.375" style="3"/>
     <col min="7" max="7" width="23.25" style="3" customWidth="1"/>
     <col min="8" max="16384" width="9" style="3"/>
@@ -1253,7 +1256,7 @@
         <v>14</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1"/>

--- a/gm/resources/sample/loginConfig.xlsx
+++ b/gm/resources/sample/loginConfig.xlsx
@@ -123,19 +123,19 @@
     <t>google登入</t>
   </si>
   <si>
-    <t>1990000_2000</t>
+    <t>1990000_8600</t>
   </si>
   <si>
     <t>ios登入</t>
   </si>
   <si>
+    <t>1990000_2100</t>
+  </si>
+  <si>
     <t>facebook登入</t>
   </si>
   <si>
     <t>手机登入</t>
-  </si>
-  <si>
-    <t>1990000_8000</t>
   </si>
 </sst>
 </file>
@@ -1228,7 +1228,7 @@
         <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" spans="1:4">
@@ -1239,10 +1239,10 @@
         <v>4</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" spans="1:4">
@@ -1253,10 +1253,10 @@
         <v>5</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1"/>

--- a/gm/resources/sample/loginConfig.xlsx
+++ b/gm/resources/sample/loginConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="loginConfig" sheetId="1" r:id="rId1"/>
@@ -123,19 +123,19 @@
     <t>google登入</t>
   </si>
   <si>
+    <t>1990000_2100</t>
+  </si>
+  <si>
+    <t>ios登入</t>
+  </si>
+  <si>
+    <t>facebook登入</t>
+  </si>
+  <si>
+    <t>手机登入</t>
+  </si>
+  <si>
     <t>1990000_8600</t>
-  </si>
-  <si>
-    <t>ios登入</t>
-  </si>
-  <si>
-    <t>1990000_2100</t>
-  </si>
-  <si>
-    <t>facebook登入</t>
-  </si>
-  <si>
-    <t>手机登入</t>
   </si>
 </sst>
 </file>
@@ -1228,7 +1228,7 @@
         <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" spans="1:4">
@@ -1239,10 +1239,10 @@
         <v>4</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" spans="1:4">
@@ -1253,10 +1253,10 @@
         <v>5</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1"/>

--- a/gm/resources/sample/loginConfig.xlsx
+++ b/gm/resources/sample/loginConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="loginConfig" sheetId="1" r:id="rId1"/>
@@ -123,7 +123,7 @@
     <t>google登入</t>
   </si>
   <si>
-    <t>1990000_2100</t>
+    <t>1990000_2000</t>
   </si>
   <si>
     <t>ios登入</t>
@@ -135,7 +135,7 @@
     <t>手机登入</t>
   </si>
   <si>
-    <t>1990000_8600</t>
+    <t>1990000_8000</t>
   </si>
 </sst>
 </file>

--- a/gm/resources/sample/loginConfig.xlsx
+++ b/gm/resources/sample/loginConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="loginConfig" sheetId="1" r:id="rId1"/>
@@ -123,7 +123,7 @@
     <t>google登入</t>
   </si>
   <si>
-    <t>1990000_2100</t>
+    <t>1990000_21400</t>
   </si>
   <si>
     <t>ios登入</t>
@@ -135,7 +135,7 @@
     <t>手机登入</t>
   </si>
   <si>
-    <t>1990000_8600</t>
+    <t>1990000_85700</t>
   </si>
 </sst>
 </file>

--- a/gm/resources/sample/loginConfig.xlsx
+++ b/gm/resources/sample/loginConfig.xlsx
@@ -123,7 +123,7 @@
     <t>google登入</t>
   </si>
   <si>
-    <t>1990000_2000</t>
+    <t>1990000_21400</t>
   </si>
   <si>
     <t>ios登入</t>
@@ -135,7 +135,7 @@
     <t>手机登入</t>
   </si>
   <si>
-    <t>1990000_8000</t>
+    <t>1990000_85700</t>
   </si>
 </sst>
 </file>
